--- a/data/trans_orig/ProblemasDormirP33b-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con problemas para dormir a diario en 2023</t>
+          <t>Población con problemas para dormir a diario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13445</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303231</t>
+          <t>301790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309890</t>
+          <t>309967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276190</t>
+          <t>275636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285645</t>
+          <t>285669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582335</t>
+          <t>582890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594922</t>
+          <t>594596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22124</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54498</t>
+          <t>50654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60418</t>
+          <t>60188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86673</t>
+          <t>86730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86958</t>
+          <t>89161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127869</t>
+          <t>126888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>467736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496266</t>
+          <t>496233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428296</t>
+          <t>428239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454551</t>
+          <t>454781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905490</t>
+          <t>906471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>946401</t>
+          <t>944198</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40236</t>
+          <t>38873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66104</t>
+          <t>64188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64317</t>
+          <t>65367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90949</t>
+          <t>91205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111119</t>
+          <t>110125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149212</t>
+          <t>146054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>249946</t>
+          <t>251862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>275814</t>
+          <t>277177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>258179</t>
+          <t>257923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284811</t>
+          <t>283761</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>515966</t>
+          <t>519124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>554059</t>
+          <t>555053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,44%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36369</t>
+          <t>35292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66302</t>
+          <t>66288</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51660</t>
+          <t>52140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116508</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102996</t>
+          <t>101611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>170622</t>
+          <t>167580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246255</t>
+          <t>246269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276188</t>
+          <t>277265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359210</t>
+          <t>359341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>424058</t>
+          <t>423578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>617652</t>
+          <t>620694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>685278</t>
+          <t>686663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12535</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>30085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166207</t>
+          <t>166386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>174926</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>237790</t>
+          <t>237420</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251518</t>
+          <t>250848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407712</t>
+          <t>407436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422671</t>
+          <t>422003</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26347</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45346</t>
+          <t>45493</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48328</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80415</t>
+          <t>79623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107901</t>
+          <t>107250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224290</t>
+          <t>224143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>243289</t>
+          <t>244081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188563</t>
+          <t>187980</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208728</t>
+          <t>208847</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418791</t>
+          <t>419442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>446277</t>
+          <t>447069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,88%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>80829</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>120296</t>
+          <t>124611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81767</t>
+          <t>77567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>221374</t>
+          <t>223355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>160077</t>
+          <t>169981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>313407</t>
+          <t>316427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>503983</t>
+          <t>499668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>544579</t>
+          <t>543450</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>627891</t>
+          <t>625910</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>767498</t>
+          <t>771698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1160137</t>
+          <t>1157117</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1313467</t>
+          <t>1303563</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58088</t>
+          <t>63881</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>190004</t>
+          <t>193121</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>194825</t>
+          <t>194238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>235184</t>
+          <t>236270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>216172</t>
+          <t>209854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>421135</t>
+          <t>422671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>738716</t>
+          <t>735599</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>870632</t>
+          <t>864839</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>482547</t>
+          <t>481461</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>522906</t>
+          <t>523493</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1225317</t>
+          <t>1223781</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1430280</t>
+          <t>1436598</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,25%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>333670</t>
+          <t>325701</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>466160</t>
+          <t>467253</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>564511</t>
+          <t>562143</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>760768</t>
+          <t>762810</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>966335</t>
+          <t>957431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1205571</t>
+          <t>1205638</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2993657</t>
+          <t>2992564</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3126147</t>
+          <t>3134116</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2951512</t>
+          <t>2949470</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3147769</t>
+          <t>3150137</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5966526</t>
+          <t>5966459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6205762</t>
+          <t>6214666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProblemasDormirP33b-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ProblemasDormirP33b-Provincia-trans_orig.xlsx
@@ -725,67 +725,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7420</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4058</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12642</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7232</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3966</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13999</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -838,69 +838,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>307458</t>
+          <t>315154</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301790</t>
+          <t>310130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309967</t>
+          <t>317470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>308641</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>303419</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>312003</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>98,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>282403</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>275636</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>285669</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>851</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>589860</t>
+          <t>623794</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582890</t>
+          <t>616810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594596</t>
+          <t>628188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33941</t>
+          <t>34865</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50654</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>72104</t>
+          <t>73659</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60188</t>
+          <t>60900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86730</t>
+          <t>87524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>106045</t>
+          <t>108524</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89161</t>
+          <t>90012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126888</t>
+          <t>131248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>484449</t>
+          <t>495782</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>467736</t>
+          <t>480157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496233</t>
+          <t>508545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442865</t>
+          <t>472835</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428239</t>
+          <t>458970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454781</t>
+          <t>485594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>927314</t>
+          <t>968617</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906471</t>
+          <t>945893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944198</t>
+          <t>987129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38873</t>
+          <t>40095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>63459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>80938</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65367</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>93142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>128256</t>
+          <t>131902</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110125</t>
+          <t>115761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146054</t>
+          <t>151729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>265109</t>
+          <t>265029</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>251862</t>
+          <t>252534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277177</t>
+          <t>275898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>271813</t>
+          <t>275443</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257923</t>
+          <t>263239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283761</t>
+          <t>287619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>536922</t>
+          <t>540473</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519124</t>
+          <t>520646</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>555053</t>
+          <t>556614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50468</t>
+          <t>58307</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35292</t>
+          <t>42707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66288</t>
+          <t>80867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89456</t>
+          <t>98915</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>84769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116377</t>
+          <t>115229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>139924</t>
+          <t>157222</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101611</t>
+          <t>134910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167580</t>
+          <t>183542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>262089</t>
+          <t>314838</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246269</t>
+          <t>292278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277265</t>
+          <t>330438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>386262</t>
+          <t>323046</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359341</t>
+          <t>306732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>423578</t>
+          <t>337192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>648350</t>
+          <t>637885</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>620694</t>
+          <t>611565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>686663</t>
+          <t>660197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>13285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30085</t>
+          <t>31379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>171392</t>
+          <t>197815</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>166386</t>
+          <t>192380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174926</t>
+          <t>201417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>243604</t>
+          <t>212665</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>237420</t>
+          <t>206642</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250848</t>
+          <t>216956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>414995</t>
+          <t>410480</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407436</t>
+          <t>403203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>422003</t>
+          <t>416576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34327</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45493</t>
+          <t>44711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58074</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48209</t>
+          <t>50893</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>71149</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>92401</t>
+          <t>94862</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79623</t>
+          <t>82211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107250</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235309</t>
+          <t>236669</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224143</t>
+          <t>225996</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>244081</t>
+          <t>244572</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>198982</t>
+          <t>202926</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187980</t>
+          <t>192601</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208847</t>
+          <t>212857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>434291</t>
+          <t>439595</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>419442</t>
+          <t>426508</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>447069</t>
+          <t>452246</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>99082</t>
+          <t>116438</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80829</t>
+          <t>93309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>124611</t>
+          <t>140824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>162789</t>
+          <t>198079</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77567</t>
+          <t>175251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223355</t>
+          <t>219431</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>261871</t>
+          <t>314517</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169981</t>
+          <t>285581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>316427</t>
+          <t>349364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>525197</t>
+          <t>603249</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>499668</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>543450</t>
+          <t>626378</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>686476</t>
+          <t>573978</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>625910</t>
+          <t>552626</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>771698</t>
+          <t>596806</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1211673</t>
+          <t>1177227</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1157117</t>
+          <t>1142380</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1303563</t>
+          <t>1206163</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>135620</t>
+          <t>151714</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>63881</t>
+          <t>131502</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>193121</t>
+          <t>173494</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>215150</t>
+          <t>242028</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>194238</t>
+          <t>217423</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>236270</t>
+          <t>263960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>350770</t>
+          <t>393743</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>209854</t>
+          <t>363982</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>422671</t>
+          <t>424086</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>793100</t>
+          <t>646358</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>735599</t>
+          <t>624578</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>864839</t>
+          <t>666570</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>502581</t>
+          <t>589303</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>481461</t>
+          <t>567371</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>523493</t>
+          <t>613908</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1295682</t>
+          <t>1235660</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1223781</t>
+          <t>1205317</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1436598</t>
+          <t>1265421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>415715</t>
+          <t>457867</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>325701</t>
+          <t>417781</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>467253</t>
+          <t>501711</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>697294</t>
+          <t>778116</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>562143</t>
+          <t>738160</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>762810</t>
+          <t>822248</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1113009</t>
+          <t>1235984</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>957431</t>
+          <t>1172707</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1205638</t>
+          <t>1295263</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3044102</t>
+          <t>3074895</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2992564</t>
+          <t>3031051</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3134116</t>
+          <t>3114981</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3014986</t>
+          <t>2958838</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2949470</t>
+          <t>2914706</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3150137</t>
+          <t>2998794</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6059088</t>
+          <t>6033732</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5966459</t>
+          <t>5974453</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6214666</t>
+          <t>6097009</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
